--- a/search/screening/fulltext/calibration_workbooks/FT_cal_R2_blank.xlsx
+++ b/search/screening/fulltext/calibration_workbooks/FT_cal_R2_blank.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全文筛选校准用工作簿（20 篇）— 筛选员 R2（卞宏强）v2026-10-17a</t>
+          <t>全文筛选校准用工作簿（20 篇）— 筛选员 R2（卞红强）v2026-10-17a</t>
         </is>
       </c>
     </row>
@@ -563,47 +563,40 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>• 每一篇都由你本人阅读全文后判断，不用任何 AI 工具、宏、脚本或自动点击（沿用标题摘要指南第 3、12 节的规定）。</t>
+          <t>• 两人都完成之前，不看对方的文件，不讨论具体的篇目。完成后另存为 FT_cal_R2.xlsx，交给杨俊保管；两人都完成后再比对。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>• 两人都完成之前，不看对方的文件，不讨论具体的篇目。完成后另存为 FT_cal_R2.xlsx，交给杨俊保管；两人都完成后再比对。</t>
+          <t>• 不要改表头、列的顺序和下拉列表（Lists 表）。不要删除 FT_log 里已填好的行；多出来的行留空即可。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>• 不要改表头、列的顺序和下拉列表（Lists 表）。不要删除 FT_log 里已填好的行；多出来的行留空即可。</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2. 说明</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2. 说明</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>• 这 20 篇在正式的全文筛选里还会再处理一遍。校准只记一致率，kappa 在 20 篇上没有意义（指南 D5）。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• 这 20 篇在正式的全文筛选里还会再处理一遍。校准只记一致率，kappa 在 20 篇上没有意义（指南 D5）。</t>
+          <t>• 指南没写清楚的情形，请记下 WS 编号和你的做法，在讨论时提出。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>• 指南没写清楚的情形，请记下 WS 编号和你的做法，在讨论时提出。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>• 这个文件没有在 Excel 或 WPS 里打开测试过：下拉列表和灰色列的显示如有问题，请告诉舒俊。</t>
         </is>
@@ -813,7 +806,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>R1 = 舒俊，R2 = 卞宏强（全文阶段），Consensus</t>
+          <t>R1 = 舒俊，R2 = 卞红强（全文阶段），Consensus</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -1516,7 +1509,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>R1 = 舒俊，R2 = 卞宏强（全文阶段）</t>
+          <t>R1 = 舒俊，R2 = 卞红强（全文阶段）</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
